--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -9019,7 +9019,7 @@
         <v>89631809</v>
       </c>
       <c r="B73" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>79134119</v>
       </c>
       <c r="B175" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>79133943</v>
       </c>
       <c r="B176" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>

--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY176"/>
+  <dimension ref="A1:AY175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8884,10 +8884,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>97608209</v>
+        <v>89631809</v>
       </c>
       <c r="B72" t="n">
-        <v>93224</v>
+        <v>57657</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8900,41 +8900,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2682</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kattuggleknallen, Hjd</t>
+          <t>Ljungdalen, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>392626.0158144586</v>
+        <v>393033</v>
       </c>
       <c r="R72" t="n">
-        <v>6968995.706471919</v>
+        <v>6969747</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8958,22 +8954,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2019-06-26</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8982,44 +8968,32 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Bäck</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>89631809</v>
+        <v>79106943</v>
       </c>
       <c r="B73" t="n">
-        <v>57657</v>
+        <v>96251</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9032,37 +9006,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>219790</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ljungdalen, Hjd</t>
+          <t>Kattuggleknallen, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>393033</v>
+        <v>392317.0292377557</v>
       </c>
       <c r="R73" t="n">
-        <v>6969747</v>
+        <v>6968886.953489108</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9086,12 +9060,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9106,26 +9090,26 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>79106943</v>
+        <v>79106455</v>
       </c>
       <c r="B74" t="n">
-        <v>96251</v>
+        <v>96336</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9138,21 +9122,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>219811</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9162,10 +9146,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>392317.0292377557</v>
+        <v>392384.9931983674</v>
       </c>
       <c r="R74" t="n">
-        <v>6968886.953489108</v>
+        <v>6968544.040459708</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -9227,7 +9211,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
+          <t>Barbara Kühn, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -9238,10 +9222,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>79106455</v>
+        <v>79106880</v>
       </c>
       <c r="B75" t="n">
-        <v>96336</v>
+        <v>93044</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9254,21 +9238,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219811</v>
+        <v>2809</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9278,10 +9262,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>392384.9931983674</v>
+        <v>392374.1918360975</v>
       </c>
       <c r="R75" t="n">
-        <v>6968544.040459708</v>
+        <v>6968800.938305348</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -9343,7 +9327,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Ulf Lindenbaum</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -9354,10 +9338,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>79106880</v>
+        <v>79106845</v>
       </c>
       <c r="B76" t="n">
-        <v>93044</v>
+        <v>89392</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9366,25 +9350,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9394,10 +9378,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>392374.1918360975</v>
+        <v>392560.1973854365</v>
       </c>
       <c r="R76" t="n">
-        <v>6968800.938305348</v>
+        <v>6968496.221964498</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -9470,10 +9454,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>79106845</v>
+        <v>79106855</v>
       </c>
       <c r="B77" t="n">
-        <v>89392</v>
+        <v>96354</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9482,25 +9466,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9510,10 +9494,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>392560.1973854365</v>
+        <v>392403.97829244</v>
       </c>
       <c r="R77" t="n">
-        <v>6968496.221964498</v>
+        <v>6968731.825467036</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -9586,10 +9570,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>79106855</v>
+        <v>79106887</v>
       </c>
       <c r="B78" t="n">
-        <v>96354</v>
+        <v>93224</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9602,21 +9586,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221952</v>
+        <v>2682</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrkammossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Helodium blandowii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9626,10 +9610,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>392403.97829244</v>
+        <v>392361.0837668337</v>
       </c>
       <c r="R78" t="n">
-        <v>6968731.825467036</v>
+        <v>6968848.010721787</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9680,6 +9664,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9702,10 +9687,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>79106887</v>
+        <v>79106910</v>
       </c>
       <c r="B79" t="n">
-        <v>93224</v>
+        <v>89406</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9714,25 +9699,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2682</v>
+        <v>1204</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kärrkammossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Helodium blandowii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(F.Weber &amp; D.Mohr) Warnst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9742,10 +9727,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>392361.0837668337</v>
+        <v>392338.8802266748</v>
       </c>
       <c r="R79" t="n">
-        <v>6968848.010721787</v>
+        <v>6968883.035005669</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9796,7 +9781,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9819,10 +9803,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79106910</v>
+        <v>79106829</v>
       </c>
       <c r="B80" t="n">
-        <v>89406</v>
+        <v>77541</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9835,21 +9819,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9859,10 +9843,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>392338.8802266748</v>
+        <v>392404.1881553147</v>
       </c>
       <c r="R80" t="n">
-        <v>6968883.035005669</v>
+        <v>6968738.220605687</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9935,10 +9919,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>79106829</v>
+        <v>79106834</v>
       </c>
       <c r="B81" t="n">
-        <v>77541</v>
+        <v>78098</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9951,21 +9935,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9975,10 +9959,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>392404.1881553147</v>
+        <v>392335.9398704009</v>
       </c>
       <c r="R81" t="n">
-        <v>6968738.220605687</v>
+        <v>6968681.927635252</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -10051,10 +10035,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>79106834</v>
+        <v>79106856</v>
       </c>
       <c r="B82" t="n">
-        <v>78098</v>
+        <v>96354</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10063,25 +10047,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10091,10 +10075,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>392335.9398704009</v>
+        <v>392336.1048662956</v>
       </c>
       <c r="R82" t="n">
-        <v>6968681.927635252</v>
+        <v>6968686.952465248</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -10167,10 +10151,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>79106856</v>
+        <v>79106928</v>
       </c>
       <c r="B83" t="n">
-        <v>96354</v>
+        <v>77506</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10179,25 +10163,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10207,10 +10191,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>392336.1048662956</v>
+        <v>392367.9900786529</v>
       </c>
       <c r="R83" t="n">
-        <v>6968686.952465248</v>
+        <v>6968849.155807628</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -10283,10 +10267,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>79106928</v>
+        <v>79106827</v>
       </c>
       <c r="B84" t="n">
-        <v>77506</v>
+        <v>77541</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10299,21 +10283,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10323,10 +10307,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>392367.9900786529</v>
+        <v>392565.1013761657</v>
       </c>
       <c r="R84" t="n">
-        <v>6968849.155807628</v>
+        <v>6968506.122290143</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -10399,10 +10383,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>79106827</v>
+        <v>79106903</v>
       </c>
       <c r="B85" t="n">
-        <v>77541</v>
+        <v>77588</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10415,21 +10399,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10439,10 +10423,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>392565.1013761657</v>
+        <v>392339.0752196613</v>
       </c>
       <c r="R85" t="n">
-        <v>6968506.122290143</v>
+        <v>6968888.973077002</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -10515,10 +10499,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>79106903</v>
+        <v>79106835</v>
       </c>
       <c r="B86" t="n">
-        <v>77588</v>
+        <v>94440</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10531,21 +10515,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>864</v>
+        <v>1841</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10555,10 +10539,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>392339.0752196613</v>
+        <v>392300.0868162134</v>
       </c>
       <c r="R86" t="n">
-        <v>6968888.973077002</v>
+        <v>6968691.793715274</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -10631,10 +10615,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>79106835</v>
+        <v>79106862</v>
       </c>
       <c r="B87" t="n">
-        <v>94440</v>
+        <v>78570</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10647,21 +10631,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1841</v>
+        <v>2081</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10671,10 +10655,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>392300.0868162134</v>
+        <v>392375.9989537356</v>
       </c>
       <c r="R87" t="n">
-        <v>6968691.793715274</v>
+        <v>6968814.140040881</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10747,10 +10731,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>79106862</v>
+        <v>79106913</v>
       </c>
       <c r="B88" t="n">
-        <v>78570</v>
+        <v>89410</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10763,21 +10747,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10787,10 +10771,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>392375.9989537356</v>
+        <v>392594.0758144793</v>
       </c>
       <c r="R88" t="n">
-        <v>6968814.140040881</v>
+        <v>6968551.819150181</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10863,10 +10847,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>79106913</v>
+        <v>79106932</v>
       </c>
       <c r="B89" t="n">
-        <v>89410</v>
+        <v>77506</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10879,21 +10863,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10903,10 +10887,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>392594.0758144793</v>
+        <v>392301.1067349287</v>
       </c>
       <c r="R89" t="n">
-        <v>6968551.819150181</v>
+        <v>6968694.961274653</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10979,10 +10963,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>79106932</v>
+        <v>79106909</v>
       </c>
       <c r="B90" t="n">
-        <v>77506</v>
+        <v>89406</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10995,21 +10979,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -11019,10 +11003,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>392301.1067349287</v>
+        <v>392324.7905737926</v>
       </c>
       <c r="R90" t="n">
-        <v>6968694.961274653</v>
+        <v>6968914.134506183</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -11095,10 +11079,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>79106909</v>
+        <v>79106851</v>
       </c>
       <c r="B91" t="n">
-        <v>89406</v>
+        <v>89338</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11111,21 +11095,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1204</v>
+        <v>112</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11135,10 +11119,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>392324.7905737926</v>
+        <v>392339.1052185595</v>
       </c>
       <c r="R91" t="n">
-        <v>6968914.134506183</v>
+        <v>6968889.886625485</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -11211,10 +11195,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>79106851</v>
+        <v>79106914</v>
       </c>
       <c r="B92" t="n">
-        <v>89338</v>
+        <v>89410</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11227,21 +11211,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11251,10 +11235,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>392339.1052185595</v>
+        <v>392717.147373996</v>
       </c>
       <c r="R92" t="n">
-        <v>6968889.886625485</v>
+        <v>6968688.181426787</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -11327,10 +11311,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>79106914</v>
+        <v>79106811</v>
       </c>
       <c r="B93" t="n">
-        <v>89410</v>
+        <v>5135</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11339,25 +11323,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11367,10 +11351,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>392717.147373996</v>
+        <v>392237.9707139181</v>
       </c>
       <c r="R93" t="n">
-        <v>6968688.181426787</v>
+        <v>6968654.964340841</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -11443,10 +11427,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>79106811</v>
+        <v>79106929</v>
       </c>
       <c r="B94" t="n">
-        <v>5135</v>
+        <v>77506</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11455,25 +11439,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11483,10 +11467,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>392237.9707139181</v>
+        <v>392394.8357102714</v>
       </c>
       <c r="R94" t="n">
-        <v>6968654.964340841</v>
+        <v>6968829.983689525</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -11559,10 +11543,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>79106929</v>
+        <v>79106879</v>
       </c>
       <c r="B95" t="n">
-        <v>77506</v>
+        <v>93044</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11571,25 +11555,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11599,10 +11583,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>392394.8357102714</v>
+        <v>392345.8917368079</v>
       </c>
       <c r="R95" t="n">
-        <v>6968829.983689525</v>
+        <v>6968971.056243866</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -11675,10 +11659,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>79106879</v>
+        <v>79106842</v>
       </c>
       <c r="B96" t="n">
-        <v>93044</v>
+        <v>89392</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11687,25 +11671,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11715,10 +11699,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>392345.8917368079</v>
+        <v>392376.118907404</v>
       </c>
       <c r="R96" t="n">
-        <v>6968971.056243866</v>
+        <v>6968817.794316118</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -11791,10 +11775,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>79106842</v>
+        <v>79106948</v>
       </c>
       <c r="B97" t="n">
-        <v>89392</v>
+        <v>5113</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11803,25 +11787,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11831,10 +11815,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>392376.118907404</v>
+        <v>392381.8479131081</v>
       </c>
       <c r="R97" t="n">
-        <v>6968817.794316118</v>
+        <v>6968824.922676076</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11907,10 +11891,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>79106948</v>
+        <v>79106927</v>
       </c>
       <c r="B98" t="n">
-        <v>5113</v>
+        <v>77506</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11919,25 +11903,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11947,10 +11931,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>392381.8479131081</v>
+        <v>392468.0548717135</v>
       </c>
       <c r="R98" t="n">
-        <v>6968824.922676076</v>
+        <v>6969010.028745129</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -12023,10 +12007,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>79106927</v>
+        <v>79106898</v>
       </c>
       <c r="B99" t="n">
-        <v>77506</v>
+        <v>77588</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12039,21 +12023,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -12063,10 +12047,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>392468.0548717135</v>
+        <v>392657.2091440751</v>
       </c>
       <c r="R99" t="n">
-        <v>6969010.028745129</v>
+        <v>6968591.824087795</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -12139,7 +12123,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>79106898</v>
+        <v>79106902</v>
       </c>
       <c r="B100" t="n">
         <v>77588</v>
@@ -12179,10 +12163,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>392657.2091440751</v>
+        <v>392304.1474392889</v>
       </c>
       <c r="R100" t="n">
-        <v>6968591.824087795</v>
+        <v>6968940.876466201</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -12255,10 +12239,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>79106902</v>
+        <v>79106945</v>
       </c>
       <c r="B101" t="n">
-        <v>77588</v>
+        <v>78602</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12267,25 +12251,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>864</v>
+        <v>6463</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12295,10 +12279,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>392304.1474392889</v>
+        <v>392377.8962439887</v>
       </c>
       <c r="R101" t="n">
-        <v>6968940.876466201</v>
+        <v>6968802.188542492</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -12371,10 +12355,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>79106945</v>
+        <v>79106937</v>
       </c>
       <c r="B102" t="n">
-        <v>78602</v>
+        <v>81236</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12383,25 +12367,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12411,10 +12395,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>392377.8962439887</v>
+        <v>392404.181379433</v>
       </c>
       <c r="R102" t="n">
-        <v>6968802.188542492</v>
+        <v>6968696.15014715</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -12487,10 +12471,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>79106937</v>
+        <v>79106832</v>
       </c>
       <c r="B103" t="n">
-        <v>81236</v>
+        <v>89356</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12499,25 +12483,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12527,10 +12511,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>392404.181379433</v>
+        <v>392300.0344991582</v>
       </c>
       <c r="R103" t="n">
-        <v>6968696.15014715</v>
+        <v>6968704.142365047</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -12603,10 +12587,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>79106832</v>
+        <v>79106923</v>
       </c>
       <c r="B104" t="n">
-        <v>89356</v>
+        <v>77506</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12615,25 +12599,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12643,10 +12627,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>392300.0344991582</v>
+        <v>392552.9592782931</v>
       </c>
       <c r="R104" t="n">
-        <v>6968704.142365047</v>
+        <v>6968512.922577982</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -12719,10 +12703,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>79106923</v>
+        <v>79106873</v>
       </c>
       <c r="B105" t="n">
-        <v>77506</v>
+        <v>73615</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12735,21 +12719,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1460</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12759,10 +12743,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>392552.9592782931</v>
+        <v>392369.9774353092</v>
       </c>
       <c r="R105" t="n">
-        <v>6968512.922577982</v>
+        <v>6968812.051320936</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12835,10 +12819,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>79106873</v>
+        <v>79106850</v>
       </c>
       <c r="B106" t="n">
-        <v>73615</v>
+        <v>89338</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12851,21 +12835,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1460</v>
+        <v>112</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12875,10 +12859,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>392369.9774353092</v>
+        <v>392326.8749995323</v>
       </c>
       <c r="R106" t="n">
-        <v>6968812.051320936</v>
+        <v>6968893.946393847</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12951,10 +12935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>79106850</v>
+        <v>79106812</v>
       </c>
       <c r="B107" t="n">
-        <v>89338</v>
+        <v>76504</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12967,21 +12951,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>112</v>
+        <v>314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12991,10 +12975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>392326.8749995323</v>
+        <v>392381.1582144941</v>
       </c>
       <c r="R107" t="n">
-        <v>6968893.946393847</v>
+        <v>6968803.91058385</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -13067,10 +13051,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>79106812</v>
+        <v>79106857</v>
       </c>
       <c r="B108" t="n">
-        <v>76504</v>
+        <v>96354</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13079,25 +13063,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>314</v>
+        <v>221952</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13107,10 +13091,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>392381.1582144941</v>
+        <v>392238.885611492</v>
       </c>
       <c r="R108" t="n">
-        <v>6968803.91058385</v>
+        <v>6968654.934272275</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -13183,10 +13167,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>79106857</v>
+        <v>79106870</v>
       </c>
       <c r="B109" t="n">
-        <v>96354</v>
+        <v>89673</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13195,25 +13179,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13223,10 +13207,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>392238.885611492</v>
+        <v>392384.1124136442</v>
       </c>
       <c r="R109" t="n">
-        <v>6968654.934272275</v>
+        <v>6968838.109303613</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -13299,10 +13283,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>79106870</v>
+        <v>79106883</v>
       </c>
       <c r="B110" t="n">
-        <v>89673</v>
+        <v>78569</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13315,21 +13299,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13339,10 +13323,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>392384.1124136442</v>
+        <v>392389.2046744322</v>
       </c>
       <c r="R110" t="n">
-        <v>6968838.109303613</v>
+        <v>6968783.983457834</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -13393,6 +13377,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -13415,10 +13400,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>79106883</v>
+        <v>79106936</v>
       </c>
       <c r="B111" t="n">
-        <v>78569</v>
+        <v>81236</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13431,21 +13416,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13455,10 +13440,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>392389.2046744322</v>
+        <v>392352.2127841326</v>
       </c>
       <c r="R111" t="n">
-        <v>6968783.983457834</v>
+        <v>6968842.814700096</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -13509,7 +13494,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -13532,10 +13516,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>79106936</v>
+        <v>79106860</v>
       </c>
       <c r="B112" t="n">
-        <v>81236</v>
+        <v>77486</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13548,21 +13532,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1312</v>
+        <v>336</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13572,10 +13556,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>392352.2127841326</v>
+        <v>392386.8125728115</v>
       </c>
       <c r="R112" t="n">
-        <v>6968842.814700096</v>
+        <v>6968780.861002307</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -13637,7 +13621,7 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Lars Gerre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13648,10 +13632,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>79106860</v>
+        <v>79106901</v>
       </c>
       <c r="B113" t="n">
-        <v>77486</v>
+        <v>77588</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13664,21 +13648,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>336</v>
+        <v>864</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13688,10 +13672,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>392386.8125728115</v>
+        <v>392451.828252492</v>
       </c>
       <c r="R113" t="n">
-        <v>6968780.861002307</v>
+        <v>6969017.876990983</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -13753,7 +13737,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Lars Gerre</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13764,10 +13748,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>79106901</v>
+        <v>79106865</v>
       </c>
       <c r="B114" t="n">
-        <v>77588</v>
+        <v>93056</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13776,25 +13760,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>864</v>
+        <v>2813</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13804,10 +13788,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>392451.828252492</v>
+        <v>392335.0640292593</v>
       </c>
       <c r="R114" t="n">
-        <v>6969017.876990983</v>
+        <v>6968975.984359726</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -13880,10 +13864,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>79106865</v>
+        <v>79106866</v>
       </c>
       <c r="B115" t="n">
-        <v>93056</v>
+        <v>73698</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13892,25 +13876,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2813</v>
+        <v>1467</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13920,10 +13904,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>392335.0640292593</v>
+        <v>392674.9828265216</v>
       </c>
       <c r="R115" t="n">
-        <v>6968975.984359726</v>
+        <v>6968813.027590357</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -13996,10 +13980,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>79106866</v>
+        <v>79106904</v>
       </c>
       <c r="B116" t="n">
-        <v>73698</v>
+        <v>77588</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -14012,21 +13996,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1467</v>
+        <v>864</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14036,10 +14020,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>392674.9828265216</v>
+        <v>392392.0162052652</v>
       </c>
       <c r="R116" t="n">
-        <v>6968813.027590357</v>
+        <v>6968827.78985378</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -14112,10 +14096,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>79106904</v>
+        <v>79106911</v>
       </c>
       <c r="B117" t="n">
-        <v>77588</v>
+        <v>89406</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14128,21 +14112,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14152,10 +14136,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>392392.0162052652</v>
+        <v>392367.9527893803</v>
       </c>
       <c r="R117" t="n">
-        <v>6968827.78985378</v>
+        <v>6968806.173176209</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -14228,10 +14212,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>79106911</v>
+        <v>79106861</v>
       </c>
       <c r="B118" t="n">
-        <v>89406</v>
+        <v>77595</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14240,25 +14224,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14268,10 +14252,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>392367.9527893803</v>
+        <v>392305.7734656254</v>
       </c>
       <c r="R118" t="n">
-        <v>6968806.173176209</v>
+        <v>6968864.917018251</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -14344,10 +14328,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>79106861</v>
+        <v>79106820</v>
       </c>
       <c r="B119" t="n">
-        <v>77595</v>
+        <v>73693</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14356,25 +14340,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6450</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14384,10 +14368,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>392305.7734656254</v>
+        <v>392349.0108271114</v>
       </c>
       <c r="R119" t="n">
-        <v>6968864.917018251</v>
+        <v>6968842.919832098</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -14460,10 +14444,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>79106820</v>
+        <v>79106946</v>
       </c>
       <c r="B120" t="n">
-        <v>73693</v>
+        <v>96336</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14472,25 +14456,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>219811</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14500,10 +14484,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>392349.0108271114</v>
+        <v>392656.856370735</v>
       </c>
       <c r="R120" t="n">
-        <v>6968842.919832098</v>
+        <v>6968595.036768529</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -14576,10 +14560,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>79106946</v>
+        <v>79106830</v>
       </c>
       <c r="B121" t="n">
-        <v>96336</v>
+        <v>77541</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14588,25 +14572,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219811</v>
+        <v>185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14616,10 +14600,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>392656.856370735</v>
+        <v>392300.1618394078</v>
       </c>
       <c r="R121" t="n">
-        <v>6968595.036768529</v>
+        <v>6968694.077723221</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -14692,10 +14676,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>79106830</v>
+        <v>79106885</v>
       </c>
       <c r="B122" t="n">
-        <v>77541</v>
+        <v>76863</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14704,25 +14688,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>185</v>
+        <v>498</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14732,10 +14716,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>392300.1618394078</v>
+        <v>392318.7698496658</v>
       </c>
       <c r="R122" t="n">
-        <v>6968694.077723221</v>
+        <v>6968967.831647771</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -14808,10 +14792,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>79106885</v>
+        <v>79106871</v>
       </c>
       <c r="B123" t="n">
-        <v>76863</v>
+        <v>89673</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14820,25 +14804,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>498</v>
+        <v>658</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14848,10 +14832,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>392318.7698496658</v>
+        <v>392369.8424797867</v>
       </c>
       <c r="R123" t="n">
-        <v>6968967.831647771</v>
+        <v>6968807.94025376</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -14924,10 +14908,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>79106871</v>
+        <v>79106908</v>
       </c>
       <c r="B124" t="n">
-        <v>89673</v>
+        <v>73678</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14936,25 +14920,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>658</v>
+        <v>6439</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14964,10 +14948,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>392369.8424797867</v>
+        <v>392305.977074551</v>
       </c>
       <c r="R124" t="n">
-        <v>6968807.94025376</v>
+        <v>6968940.816364875</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -15040,10 +15024,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>79106908</v>
+        <v>79106897</v>
       </c>
       <c r="B125" t="n">
-        <v>73678</v>
+        <v>78527</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -15056,21 +15040,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6439</v>
+        <v>229497</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15080,10 +15064,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>392305.977074551</v>
+        <v>392394.1164779942</v>
       </c>
       <c r="R125" t="n">
-        <v>6968940.816364875</v>
+        <v>6968780.164001447</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -15156,10 +15140,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>79106897</v>
+        <v>79106884</v>
       </c>
       <c r="B126" t="n">
-        <v>78527</v>
+        <v>76863</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15168,25 +15152,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229497</v>
+        <v>498</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15196,10 +15180,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>392394.1164779942</v>
+        <v>392674.1637984799</v>
       </c>
       <c r="R126" t="n">
-        <v>6968780.164001447</v>
+        <v>6968829.973492629</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -15272,10 +15256,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>79106884</v>
+        <v>79106882</v>
       </c>
       <c r="B127" t="n">
-        <v>76863</v>
+        <v>78569</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15284,25 +15268,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>498</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15312,10 +15296,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>392674.1637984799</v>
+        <v>392365.9131409845</v>
       </c>
       <c r="R127" t="n">
-        <v>6968829.973492629</v>
+        <v>6968799.838235305</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -15388,10 +15372,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>79106882</v>
+        <v>79106863</v>
       </c>
       <c r="B128" t="n">
-        <v>78569</v>
+        <v>78570</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15404,21 +15388,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15428,10 +15412,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>392365.9131409845</v>
+        <v>392395.0313402535</v>
       </c>
       <c r="R128" t="n">
-        <v>6968799.838235305</v>
+        <v>6968780.133976152</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -15504,10 +15488,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>79106863</v>
+        <v>79106875</v>
       </c>
       <c r="B129" t="n">
-        <v>78570</v>
+        <v>73615</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15520,21 +15504,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>1460</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15544,10 +15528,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>392395.0313402535</v>
+        <v>392393.12665684</v>
       </c>
       <c r="R129" t="n">
-        <v>6968780.133976152</v>
+        <v>6968777.910079434</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -15620,10 +15604,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>79106875</v>
+        <v>79106931</v>
       </c>
       <c r="B130" t="n">
-        <v>73615</v>
+        <v>77506</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15636,21 +15620,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1460</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15660,10 +15644,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>392393.12665684</v>
+        <v>392336.1048662956</v>
       </c>
       <c r="R130" t="n">
-        <v>6968777.910079434</v>
+        <v>6968686.952465248</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -15736,10 +15720,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>79106931</v>
+        <v>79106844</v>
       </c>
       <c r="B131" t="n">
-        <v>77506</v>
+        <v>89392</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15752,21 +15736,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15776,10 +15760,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>392336.1048662956</v>
+        <v>392370.8622988779</v>
       </c>
       <c r="R131" t="n">
-        <v>6968686.952465248</v>
+        <v>6968811.107718782</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -15852,10 +15836,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>79106844</v>
+        <v>79106854</v>
       </c>
       <c r="B132" t="n">
-        <v>89392</v>
+        <v>96354</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15864,25 +15848,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15892,10 +15876,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>392370.8622988779</v>
+        <v>392317.0292377557</v>
       </c>
       <c r="R132" t="n">
-        <v>6968811.107718782</v>
+        <v>6968886.953489108</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -15968,10 +15952,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>79106854</v>
+        <v>79106849</v>
       </c>
       <c r="B133" t="n">
-        <v>96354</v>
+        <v>78596</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15984,21 +15968,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -16008,10 +15992,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>392317.0292377557</v>
+        <v>392397.116315471</v>
       </c>
       <c r="R133" t="n">
-        <v>6968886.953489108</v>
+        <v>6968759.945108059</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -16084,10 +16068,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>79106849</v>
+        <v>79106859</v>
       </c>
       <c r="B134" t="n">
-        <v>78596</v>
+        <v>77486</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16096,25 +16080,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>336</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -16124,10 +16108,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>392397.116315471</v>
+        <v>392299.8657054514</v>
       </c>
       <c r="R134" t="n">
-        <v>6968759.945108059</v>
+        <v>6968935.987255738</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -16189,7 +16173,7 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Lars Gerre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -16200,10 +16184,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>79106859</v>
+        <v>79106843</v>
       </c>
       <c r="B135" t="n">
-        <v>77486</v>
+        <v>89392</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16216,21 +16200,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>336</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16240,10 +16224,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>392299.8657054514</v>
+        <v>392383.1975675372</v>
       </c>
       <c r="R135" t="n">
-        <v>6968935.987255738</v>
+        <v>6968838.139332097</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -16305,7 +16289,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Lars Gerre</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -16316,10 +16300,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>79106843</v>
+        <v>79106818</v>
       </c>
       <c r="B136" t="n">
-        <v>89392</v>
+        <v>73693</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -16332,21 +16316,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -16356,10 +16340,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>392383.1975675372</v>
+        <v>392468.0848349635</v>
       </c>
       <c r="R136" t="n">
-        <v>6968838.139332097</v>
+        <v>6969010.942259666</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -16432,10 +16416,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>79106818</v>
+        <v>79106837</v>
       </c>
       <c r="B137" t="n">
-        <v>73693</v>
+        <v>78072</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -16448,21 +16432,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6440</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -16472,10 +16456,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>392468.0848349635</v>
+        <v>392335.9398704009</v>
       </c>
       <c r="R137" t="n">
-        <v>6969010.942259666</v>
+        <v>6968681.927635252</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -16548,10 +16532,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>79106837</v>
+        <v>79106809</v>
       </c>
       <c r="B138" t="n">
-        <v>78072</v>
+        <v>103250</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -16560,25 +16544,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>221725</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -16588,10 +16572,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>392335.9398704009</v>
+        <v>392378.0374272109</v>
       </c>
       <c r="R138" t="n">
-        <v>6968681.927635252</v>
+        <v>6968987.833747219</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -16664,10 +16648,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>79106809</v>
+        <v>79106905</v>
       </c>
       <c r="B139" t="n">
-        <v>103250</v>
+        <v>78533</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -16680,21 +16664,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221725</v>
+        <v>229748</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -16704,10 +16688,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>392378.0374272109</v>
+        <v>392390.0589134901</v>
       </c>
       <c r="R139" t="n">
-        <v>6968987.833747219</v>
+        <v>6968837.914124703</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -16780,10 +16764,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>79106905</v>
+        <v>79106930</v>
       </c>
       <c r="B140" t="n">
-        <v>78533</v>
+        <v>77506</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -16792,25 +16776,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16820,10 +16804,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>392390.0589134901</v>
+        <v>392386.9035006259</v>
       </c>
       <c r="R140" t="n">
-        <v>6968837.914124703</v>
+        <v>6968699.918224241</v>
       </c>
       <c r="S140" t="n">
         <v>15</v>
@@ -16896,10 +16880,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>79106930</v>
+        <v>79106949</v>
       </c>
       <c r="B141" t="n">
-        <v>77506</v>
+        <v>5113</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -16908,25 +16892,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16936,10 +16920,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>392386.9035006259</v>
+        <v>392238.9156377392</v>
       </c>
       <c r="R141" t="n">
-        <v>6968699.918224241</v>
+        <v>6968655.847886033</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -17012,10 +16996,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>79106949</v>
+        <v>79106828</v>
       </c>
       <c r="B142" t="n">
-        <v>5113</v>
+        <v>77541</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -17024,25 +17008,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -17052,10 +17036,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>392238.9156377392</v>
+        <v>392392.8618427634</v>
       </c>
       <c r="R142" t="n">
-        <v>6968655.847886033</v>
+        <v>6968979.116579589</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -17128,10 +17112,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>79106828</v>
+        <v>79134143</v>
       </c>
       <c r="B143" t="n">
-        <v>77541</v>
+        <v>96254</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -17140,41 +17124,49 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>185</v>
+        <v>223597</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kattuggleknallen, Hjd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>392392.8618427634</v>
+        <v>392306.7722910416</v>
       </c>
       <c r="R143" t="n">
-        <v>6968979.116579589</v>
+        <v>6968965.024934197</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17216,38 +17208,40 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Cirka antal.</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>79134143</v>
+        <v>79134028</v>
       </c>
       <c r="B144" t="n">
-        <v>96254</v>
+        <v>77506</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -17256,35 +17250,30 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
@@ -17292,10 +17281,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>392306.7722910416</v>
+        <v>392325.0377110224</v>
       </c>
       <c r="R144" t="n">
-        <v>6968965.024934197</v>
+        <v>6968879.831447978</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17342,7 +17331,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Cirka antal.</t>
+          <t>Ganska mycket på gammal gran.</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17370,10 +17359,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>79134028</v>
+        <v>79134456</v>
       </c>
       <c r="B145" t="n">
-        <v>77506</v>
+        <v>96336</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -17382,30 +17371,39 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>219811</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
@@ -17413,10 +17411,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>392325.0377110224</v>
+        <v>392705.0772981263</v>
       </c>
       <c r="R145" t="n">
-        <v>6968879.831447978</v>
+        <v>6968795.123432802</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17463,7 +17461,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Ganska mycket på gammal gran.</t>
+          <t>Blommande. Cirka antal.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17491,7 +17489,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>79134456</v>
+        <v>79134601</v>
       </c>
       <c r="B146" t="n">
         <v>96336</v>
@@ -17524,11 +17522,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -17543,13 +17537,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>392705.0772981263</v>
+        <v>392649.9584386861</v>
       </c>
       <c r="R146" t="n">
-        <v>6968795.123432802</v>
+        <v>6968580.171515227</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17593,7 +17587,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Blommande. Cirka antal.</t>
+          <t>Flera blommande observerade.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17621,10 +17615,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>79134601</v>
+        <v>79138744</v>
       </c>
       <c r="B147" t="n">
-        <v>96336</v>
+        <v>76504</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -17633,35 +17627,30 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>219811</v>
+        <v>314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
@@ -17669,13 +17658,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>392649.9584386861</v>
+        <v>392288.9223656831</v>
       </c>
       <c r="R147" t="n">
-        <v>6968580.171515227</v>
+        <v>6968784.075402739</v>
       </c>
       <c r="S147" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17715,11 +17704,6 @@
       <c r="AB147" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Flera blommande observerade.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17732,22 +17716,51 @@
       <c r="AG147" t="b">
         <v>0</v>
       </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>mix av lågört och blåbär</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr"/>
+          <t>Janolof Hermansson, Helena Björnström, Lars Gerre, Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>79138744</v>
+        <v>79138793</v>
       </c>
       <c r="B148" t="n">
         <v>76504</v>
@@ -17790,10 +17803,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>392288.9223656831</v>
+        <v>392299.8657054514</v>
       </c>
       <c r="R148" t="n">
-        <v>6968784.075402739</v>
+        <v>6968935.987255738</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -17892,10 +17905,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>79138793</v>
+        <v>79138879</v>
       </c>
       <c r="B149" t="n">
-        <v>76504</v>
+        <v>81236</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -17908,21 +17921,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>314</v>
+        <v>1312</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17935,10 +17948,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>392299.8657054514</v>
+        <v>392407.2258314198</v>
       </c>
       <c r="R149" t="n">
-        <v>6968935.987255738</v>
+        <v>6968705.19608893</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18005,17 +18018,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr"/>
@@ -18037,10 +18050,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>79138879</v>
+        <v>79138729</v>
       </c>
       <c r="B150" t="n">
-        <v>81236</v>
+        <v>73473</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -18049,25 +18062,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1312</v>
+        <v>98</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -18080,10 +18093,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>392407.2258314198</v>
+        <v>392288.9223656831</v>
       </c>
       <c r="R150" t="n">
-        <v>6968705.19608893</v>
+        <v>6968784.075402739</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18128,6 +18141,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
@@ -18150,17 +18168,17 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr"/>
@@ -18182,10 +18200,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>79138729</v>
+        <v>79138961</v>
       </c>
       <c r="B151" t="n">
-        <v>73473</v>
+        <v>78533</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -18194,25 +18212,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>98</v>
+        <v>229748</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -18225,10 +18243,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>392288.9223656831</v>
+        <v>392270.793757025</v>
       </c>
       <c r="R151" t="n">
-        <v>6968784.075402739</v>
+        <v>6968929.168963158</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -18271,11 +18289,6 @@
       <c r="AB151" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18332,10 +18345,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>79138961</v>
+        <v>79138757</v>
       </c>
       <c r="B152" t="n">
-        <v>78533</v>
+        <v>73687</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -18344,25 +18357,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>229748</v>
+        <v>309</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Parknål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca hispidula</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Zahlbr.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -18375,10 +18388,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>392270.793757025</v>
+        <v>392288.9223656831</v>
       </c>
       <c r="R152" t="n">
-        <v>6968929.168963158</v>
+        <v>6968784.075402739</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18477,10 +18490,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>79138757</v>
+        <v>79138889</v>
       </c>
       <c r="B153" t="n">
-        <v>73687</v>
+        <v>77506</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -18493,21 +18506,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>309</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Parknål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca hispidula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -18520,10 +18533,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>392288.9223656831</v>
+        <v>392407.2258314198</v>
       </c>
       <c r="R153" t="n">
-        <v>6968784.075402739</v>
+        <v>6968705.19608893</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18590,17 +18603,17 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr"/>
@@ -18622,10 +18635,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>79138889</v>
+        <v>79138953</v>
       </c>
       <c r="B154" t="n">
-        <v>77506</v>
+        <v>78527</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -18634,25 +18647,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -18665,10 +18678,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>392407.2258314198</v>
+        <v>392270.793757025</v>
       </c>
       <c r="R154" t="n">
-        <v>6968705.19608893</v>
+        <v>6968929.168963158</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18713,6 +18726,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
@@ -18735,17 +18753,17 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr"/>
@@ -18767,10 +18785,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>79138953</v>
+        <v>79106848</v>
       </c>
       <c r="B155" t="n">
-        <v>78527</v>
+        <v>4711</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -18783,26 +18801,32 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>229497</v>
+        <v>100299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -18810,13 +18834,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>392270.793757025</v>
+        <v>392380.9030762318</v>
       </c>
       <c r="R155" t="n">
-        <v>6968929.168963158</v>
+        <v>6968824.039138732</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18856,11 +18880,6 @@
       <c r="AB155" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18873,40 +18892,15 @@
       <c r="AG155" t="b">
         <v>0</v>
       </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>mix av lågört och blåbär</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Helena Björnström, Lars Gerre, Elin Götmark</t>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -18917,48 +18911,42 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>79106848</v>
+        <v>79138784</v>
       </c>
       <c r="B156" t="n">
-        <v>4711</v>
+        <v>73473</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100299</v>
+        <v>98</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mörk rödprick</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Arthonia incarnata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Th.Fr. ex Almq.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -18966,13 +18954,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>392380.9030762318</v>
+        <v>392299.8657054514</v>
       </c>
       <c r="R156" t="n">
-        <v>6968824.039138732</v>
+        <v>6968935.987255738</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -19012,6 +19000,11 @@
       <c r="AB156" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19024,15 +19017,40 @@
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>mix av lågört och blåbär</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
+          <t>Janolof Hermansson, Helena Björnström, Lars Gerre, Elin Götmark</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -19043,37 +19061,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>79138784</v>
+        <v>81014945</v>
       </c>
       <c r="B157" t="n">
-        <v>73473</v>
+        <v>77486</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>98</v>
+        <v>336</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk rödprick</t>
+          <t>Solfjäderlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Arthonia incarnata</t>
+          <t>Cheiromycina flabelliformis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Th.Fr. ex Almq.</t>
+          <t>B.Sutton</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -19086,13 +19104,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>392299.8657054514</v>
+        <v>392378.7135245515</v>
       </c>
       <c r="R157" t="n">
-        <v>6968935.987255738</v>
+        <v>6968813.136380884</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19132,11 +19150,6 @@
       <c r="AB157" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19149,58 +19162,54 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>mix av lågört och blåbär</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+          <t>barrblandskog</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>bark av gammal sälg</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>bark av gammal sälg</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>L18</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Helena Björnström, Lars Gerre, Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Elin Götmark</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>81014945</v>
+        <v>79106847</v>
       </c>
       <c r="B158" t="n">
-        <v>77486</v>
+        <v>56395</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19209,40 +19218,37 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>336</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Solfjäderlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cheiromycina flabelliformis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>B.Sutton</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Kattuggleknallen, Hjd</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>392378.7135245515</v>
+        <v>392704.0280852083</v>
       </c>
       <c r="R158" t="n">
-        <v>6968813.136380884</v>
+        <v>6968651.112650151</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -19284,103 +19290,86 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
-      </c>
-      <c r="AL158" t="inlineStr">
-        <is>
-          <t>bark av gammal sälg</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>bark av gammal sälg</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>L18</t>
-        </is>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>79106847</v>
+        <v>89632043</v>
       </c>
       <c r="B159" t="n">
-        <v>56395</v>
+        <v>78602</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Kattuggleknallen, Hjd</t>
+          <t>Ljungdalen, Hjd</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>392704.0280852083</v>
+        <v>392222.0240999116</v>
       </c>
       <c r="R159" t="n">
-        <v>6968651.112650151</v>
+        <v>6968949.976812804</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -19404,7 +19393,7 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
@@ -19414,17 +19403,12 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>2020-06-28</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -19439,26 +19423,26 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Barbara Kühn, Helena Björnström, Janolof Hermansson, Elin Götmark, Lars Gerre</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>89632043</v>
+        <v>89632044</v>
       </c>
       <c r="B160" t="n">
-        <v>78602</v>
+        <v>78596</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -19471,21 +19455,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -19495,10 +19479,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>392222.0240999116</v>
+        <v>392220.8389970732</v>
       </c>
       <c r="R160" t="n">
-        <v>6968949.976812804</v>
+        <v>6968941.785089125</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -19571,10 +19555,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>89632044</v>
+        <v>89632201</v>
       </c>
       <c r="B161" t="n">
-        <v>78596</v>
+        <v>89392</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -19583,25 +19567,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -19611,10 +19595,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>392220.8389970732</v>
+        <v>392411.9973892733</v>
       </c>
       <c r="R161" t="n">
-        <v>6968941.785089125</v>
+        <v>6969004.094665608</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19687,10 +19671,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>89632201</v>
+        <v>89632222</v>
       </c>
       <c r="B162" t="n">
-        <v>89392</v>
+        <v>96354</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -19699,25 +19683,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -19727,10 +19711,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>392411.9973892733</v>
+        <v>392615.1230983305</v>
       </c>
       <c r="R162" t="n">
-        <v>6969004.094665608</v>
+        <v>6968593.20212938</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19803,10 +19787,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>89632222</v>
+        <v>89632224</v>
       </c>
       <c r="B163" t="n">
-        <v>96354</v>
+        <v>78570</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -19815,25 +19799,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -19843,10 +19827,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>392615.1230983305</v>
+        <v>392632.0966657351</v>
       </c>
       <c r="R163" t="n">
-        <v>6968593.20212938</v>
+        <v>6968733.950487081</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19919,10 +19903,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>89632224</v>
+        <v>89632196</v>
       </c>
       <c r="B164" t="n">
-        <v>78570</v>
+        <v>81236</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -19935,21 +19919,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -19959,10 +19943,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>392632.0966657351</v>
+        <v>392416.210985308</v>
       </c>
       <c r="R164" t="n">
-        <v>6968733.950487081</v>
+        <v>6968644.080914029</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -20035,10 +20019,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>89632196</v>
+        <v>89631986</v>
       </c>
       <c r="B165" t="n">
-        <v>81236</v>
+        <v>85703</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -20051,21 +20035,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -20075,10 +20059,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>392416.210985308</v>
+        <v>392214.0760849837</v>
       </c>
       <c r="R165" t="n">
-        <v>6968644.080914029</v>
+        <v>6968958.926029278</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -20151,10 +20135,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>89631986</v>
+        <v>89632197</v>
       </c>
       <c r="B166" t="n">
-        <v>85703</v>
+        <v>93044</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -20163,25 +20147,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>510</v>
+        <v>2809</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -20191,10 +20175,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>392214.0760849837</v>
+        <v>392354.0050393018</v>
       </c>
       <c r="R166" t="n">
-        <v>6968958.926029278</v>
+        <v>6968967.131794748</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -20267,10 +20251,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>89632197</v>
+        <v>89632199</v>
       </c>
       <c r="B167" t="n">
-        <v>93044</v>
+        <v>77506</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -20279,25 +20263,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -20307,10 +20291,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>392354.0050393018</v>
+        <v>392469.9873321084</v>
       </c>
       <c r="R167" t="n">
-        <v>6968967.131794748</v>
+        <v>6968650.090977598</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20383,10 +20367,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>89632199</v>
+        <v>89632223</v>
       </c>
       <c r="B168" t="n">
-        <v>77506</v>
+        <v>89410</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -20399,21 +20383,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -20423,10 +20407,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>392469.9873321084</v>
+        <v>392632.9454381638</v>
       </c>
       <c r="R168" t="n">
-        <v>6968650.090977598</v>
+        <v>6968717.917667629</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -20499,10 +20483,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>89632223</v>
+        <v>89632227</v>
       </c>
       <c r="B169" t="n">
-        <v>89410</v>
+        <v>78596</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -20511,25 +20495,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -20539,10 +20523,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>392632.9454381638</v>
+        <v>392632.1564994607</v>
       </c>
       <c r="R169" t="n">
-        <v>6968717.917667629</v>
+        <v>6968735.777668556</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20615,10 +20599,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>89632227</v>
+        <v>89632106</v>
       </c>
       <c r="B170" t="n">
-        <v>78596</v>
+        <v>93044</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -20631,21 +20615,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -20655,10 +20639,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>392632.1564994607</v>
+        <v>392382.0480875829</v>
       </c>
       <c r="R170" t="n">
-        <v>6968735.777668556</v>
+        <v>6969151.85172828</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20731,10 +20715,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>89632106</v>
+        <v>89632105</v>
       </c>
       <c r="B171" t="n">
-        <v>93044</v>
+        <v>89356</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -20747,21 +20731,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -20771,10 +20755,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>392382.0480875829</v>
+        <v>392550.2078816181</v>
       </c>
       <c r="R171" t="n">
-        <v>6969151.85172828</v>
+        <v>6968498.835884367</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20847,10 +20831,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>89632105</v>
+        <v>89632195</v>
       </c>
       <c r="B172" t="n">
-        <v>89356</v>
+        <v>92505</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -20863,34 +20847,38 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5447</v>
+        <v>2412</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Ljungdalen, Hjd</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>392550.2078816181</v>
+        <v>392549.8411689595</v>
       </c>
       <c r="R172" t="n">
-        <v>6968498.835884367</v>
+        <v>6968725.212931252</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20941,6 +20929,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -20963,10 +20952,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>89632195</v>
+        <v>89632221</v>
       </c>
       <c r="B173" t="n">
-        <v>92505</v>
+        <v>89392</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -20975,42 +20964,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2412</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Ljungdalen, Hjd</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>392549.8411689595</v>
+        <v>392649.0816707878</v>
       </c>
       <c r="R173" t="n">
-        <v>6968725.212931252</v>
+        <v>6968735.223472802</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -21061,7 +21046,6 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
@@ -21084,10 +21068,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>89632221</v>
+        <v>79133943</v>
       </c>
       <c r="B174" t="n">
-        <v>89392</v>
+        <v>57657</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -21096,41 +21080,49 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Ljungdalen, Hjd</t>
+          <t>Kattuggleknallen, Hjd</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>392649.0816707878</v>
+        <v>392350</v>
       </c>
       <c r="R174" t="n">
-        <v>6968735.223472802</v>
+        <v>6968685</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -21154,22 +21146,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-26</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -21184,23 +21166,19 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>79133943</v>
+        <v>79134119</v>
       </c>
       <c r="B175" t="n">
         <v>57657</v>
@@ -21240,7 +21218,11 @@
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
@@ -21248,10 +21230,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>392350</v>
+        <v>392280</v>
       </c>
       <c r="R175" t="n">
-        <v>6968685</v>
+        <v>6968920</v>
       </c>
       <c r="S175" t="n">
         <v>25</v>
@@ -21286,6 +21268,11 @@
           <t>2019-07-26</t>
         </is>
       </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>I gammal granskog.</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
@@ -21307,125 +21294,6 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>79134119</v>
-      </c>
-      <c r="B176" t="n">
-        <v>57657</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr"/>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>Kattuggleknallen, Hjd</t>
-        </is>
-      </c>
-      <c r="Q176" t="n">
-        <v>392280</v>
-      </c>
-      <c r="R176" t="n">
-        <v>6968920</v>
-      </c>
-      <c r="S176" t="n">
-        <v>25</v>
-      </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V176" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y176" t="inlineStr">
-        <is>
-          <t>2019-07-26</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>2019-07-26</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>I gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AD176" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE176" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG176" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT176" t="inlineStr"/>
-      <c r="AW176" t="inlineStr">
-        <is>
-          <t>Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AX176" t="inlineStr">
-        <is>
-          <t>Lars Gerre</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32323-2023 artfynd.xlsx
+++ b/artfynd/A 32323-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY185"/>
+  <dimension ref="A1:AZ185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632137</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106899</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106900</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632113</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632218</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106839</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106840</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106841</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106846</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631832</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632121</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631806</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632109</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632132</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2495,6 +2585,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632123</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631799</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631814</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2798,6 +2903,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632112</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2899,6 +3009,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631798</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3005,6 +3120,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631803</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3106,6 +3226,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631824</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3207,6 +3332,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631839</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3306,6 +3436,11 @@
       <c r="AY27" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632127</t>
         </is>
       </c>
     </row>
@@ -3413,6 +3548,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632128</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3514,6 +3654,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632129</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3615,6 +3760,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632136</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3716,6 +3866,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632229</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3817,6 +3972,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632231</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3923,6 +4083,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632232</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4024,6 +4189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106890</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4125,6 +4295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106891</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4226,6 +4401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106892</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4326,6 +4506,11 @@
       <c r="AY37" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106886</t>
         </is>
       </c>
     </row>
@@ -4445,6 +4630,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97608209</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4546,6 +4736,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106864</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4645,6 +4840,11 @@
       <c r="AY40" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106926</t>
         </is>
       </c>
     </row>
@@ -4777,6 +4977,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79139032</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4878,6 +5083,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632117</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4979,6 +5189,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632125</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5080,6 +5295,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632220</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5181,6 +5401,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631830</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5282,6 +5507,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631836</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5383,6 +5613,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632108</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5489,6 +5724,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632131</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5590,6 +5830,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632202</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5691,6 +5936,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632120</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5792,6 +6042,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632111</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5893,6 +6148,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632114</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5994,6 +6254,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632116</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6095,6 +6360,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632118</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6196,6 +6466,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632119</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6297,6 +6572,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632230</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6398,6 +6678,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631808</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6499,6 +6784,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632110</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6600,6 +6890,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631819</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6701,6 +6996,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632124</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6811,6 +7111,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134219</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6921,6 +7226,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134421</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7027,6 +7337,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632135</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7128,6 +7443,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632193</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7229,6 +7549,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632204</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7339,6 +7664,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134189</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7438,6 +7768,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631809</t>
         </is>
       </c>
     </row>
@@ -7545,6 +7880,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134383</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7646,6 +7986,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632228</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7761,6 +8106,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134268</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7862,6 +8212,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632133</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7963,6 +8318,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632194</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8064,6 +8424,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631838</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8163,6 +8528,11 @@
       <c r="AY74" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106836</t>
         </is>
       </c>
     </row>
@@ -8300,6 +8670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138729</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8435,6 +8810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138784</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8536,6 +8916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106850</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8637,6 +9022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106851</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8739,6 +9129,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106823</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8840,6 +9235,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106827</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8941,6 +9341,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106828</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9042,6 +9447,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106829</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9141,6 +9551,11 @@
       <c r="AY83" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106830</t>
         </is>
       </c>
     </row>
@@ -9273,6 +9688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138757</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9372,6 +9792,11 @@
       <c r="AY85" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106812</t>
         </is>
       </c>
     </row>
@@ -9504,6 +9929,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138744</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9634,6 +10064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138793</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9735,6 +10170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106884</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9836,6 +10276,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106885</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9937,6 +10382,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89631986</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10038,6 +10488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106870</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10139,6 +10594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106871</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10240,6 +10700,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106898</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10341,6 +10806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106901</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10442,6 +10912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106902</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10543,6 +11018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106903</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10644,6 +11124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106904</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10745,6 +11230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106842</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10846,6 +11336,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106843</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10947,6 +11442,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106844</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11048,6 +11548,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106845</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11149,6 +11654,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632201</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11250,6 +11760,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632221</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11351,6 +11866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106909</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11452,6 +11972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106910</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11553,6 +12078,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106911</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11654,6 +12184,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632182</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11755,6 +12290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106936</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11854,6 +12394,11 @@
       <c r="AY109" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106937</t>
         </is>
       </c>
     </row>
@@ -11986,6 +12531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138879</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12087,6 +12637,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632196</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12188,6 +12743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106873</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12289,6 +12849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106875</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12390,6 +12955,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106866</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12491,6 +13061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106835</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12592,6 +13167,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106862</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12693,6 +13273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106863</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12792,6 +13377,11 @@
       <c r="AY118" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632224</t>
         </is>
       </c>
     </row>
@@ -12900,6 +13490,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632195</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13002,6 +13597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106887</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13103,6 +13703,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106879</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13204,6 +13809,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106880</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13305,6 +13915,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632106</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13406,6 +14021,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632197</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13507,6 +14127,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106865</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13608,6 +14233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106832</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13709,6 +14339,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632105</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13810,6 +14445,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106923</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13911,6 +14551,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106925</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14012,6 +14657,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106927</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14113,6 +14763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106928</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14214,6 +14869,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106929</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14315,6 +14975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106930</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14416,6 +15081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106931</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14517,6 +15187,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106932</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14616,6 +15291,11 @@
       <c r="AY136" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106933</t>
         </is>
       </c>
     </row>
@@ -14724,6 +15404,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134028</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14854,6 +15539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138889</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14955,6 +15645,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632199</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15056,6 +15751,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106908</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15158,6 +15858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106816</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15259,6 +15964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106818</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15360,6 +16070,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106820</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15461,6 +16176,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632208</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15562,6 +16282,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632215</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15663,6 +16388,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632217</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15764,6 +16494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106861</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15865,6 +16600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106834</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15966,6 +16706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106882</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16068,6 +16813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106883</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16169,6 +16919,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106849</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16270,6 +17025,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632044</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16371,6 +17131,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632227</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16472,6 +17237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106945</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16573,6 +17343,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632043</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16679,6 +17454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106847</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16783,6 +17563,11 @@
       <c r="AY157" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632213</t>
         </is>
       </c>
     </row>
@@ -16896,6 +17681,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106848</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16997,6 +17787,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106948</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17096,6 +17891,11 @@
       <c r="AY160" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106949</t>
         </is>
       </c>
     </row>
@@ -17203,6 +18003,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79133943</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17317,6 +18122,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134119</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17427,6 +18237,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79133966</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17528,6 +18343,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632048</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17629,6 +18449,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106811</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17730,6 +18555,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106943</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17831,6 +18661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106455</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17932,6 +18767,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106946</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18047,6 +18887,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134456</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18158,6 +19003,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134601</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18259,6 +19109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106809</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18360,6 +19215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106854</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18461,6 +19321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106855</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18562,6 +19427,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106856</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18663,6 +19533,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106857</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18762,6 +19637,11 @@
       <c r="AY176" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89632222</t>
         </is>
       </c>
     </row>
@@ -18884,6 +19764,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293276</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19002,6 +19887,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293332</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19113,6 +20003,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79134143</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19212,6 +20107,11 @@
       <c r="AY180" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106897</t>
         </is>
       </c>
     </row>
@@ -19349,6 +20249,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138953</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19479,6 +20384,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79139053</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19578,6 +20488,11 @@
       <c r="AY183" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106905</t>
         </is>
       </c>
     </row>
@@ -19710,6 +20625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79138961</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19811,8 +20731,199 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79106837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>